--- a/full/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/full/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rb89ec77687b84a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="R8b74f47a1aa24ba5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fb743ae78594794"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94d9749346b46d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/full/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/full/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="R8b74f47a1aa24ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rb5f714c30f494d6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94d9749346b46d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R214b1126801b4098"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/full/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/full/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rb5f714c30f494d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="R422fcaf9f4d846d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R214b1126801b4098"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d71b58246bb454b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/full/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/full/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="R422fcaf9f4d846d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rb3af2ca51be24668"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -470,7 +470,7 @@
       <x:c r="C11" s="6" t="str"/>
       <x:c r="D11" s="6" t="str"/>
       <x:c r="E11" s="5" t="str">
-        <x:v>Historical branch-like reference; locality unresolved.</x:v>
+        <x:v>Probable source variant of Cog/Cogan; exact cause of the spelling difference unresolved.</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str"/>
       <x:c r="G11" s="5" t="str"/>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d71b58246bb454b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1edf0a3d6ca94135"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/full/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/full/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rb3af2ca51be24668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rc6499bf10df14490"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1edf0a3d6ca94135"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65a9fd4932b48ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/full/exports/Welsh-LDS-Possible-Branches.xlsx
+++ b/full/exports/Welsh-LDS-Possible-Branches.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="Rc6499bf10df14490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible" sheetId="1" r:id="R2308bd3b3af04773"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,7 +801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65a9fd4932b48ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a18e825d664a1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>